--- a/tasks/finalpool/terminal-sf-wc-order-audit-excel-word/groundtruth_workspace/Order_Audit_Report.xlsx
+++ b/tasks/finalpool/terminal-sf-wc-order-audit-excel-word/groundtruth_workspace/Order_Audit_Report.xlsx
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>411.41</v>
       </c>
     </row>
   </sheetData>
@@ -712,10 +712,10 @@
         <v>152.45</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>411.41</v>
       </c>
       <c r="D3" t="n">
-        <v>152.45</v>
+        <v>-258.96</v>
       </c>
     </row>
     <row r="4">
@@ -728,10 +728,10 @@
         <v>3048998.33</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>61712.04</v>
       </c>
       <c r="D4" t="n">
-        <v>3048998.33</v>
+        <v>2987286.29</v>
       </c>
     </row>
   </sheetData>
